--- a/predictions.xlsx
+++ b/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B237"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2800,6 +2800,266 @@
         <v>1</v>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>609_0_4_第1班</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>609_0_4_第2班</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>609_0_4_第3班</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>609_0_4_第4班</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>609_0_4_第5班</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>609_0_4_第6班</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>609_0_4_第7班</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>609_0_4_第8班</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>609_0_4_第9班</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>609_0_4_第10班</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>609_0_4_第11班</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>609_0_4_第12班</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>609_0_4_第13班</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>609_0_5_第1班</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>609_0_5_第2班</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>609_0_5_第3班</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>609_0_5_第4班</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>609_0_5_第5班</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>609_0_5_第6班</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>609_0_5_第7班</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>609_0_5_第8班</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>609_0_5_第9班</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>609_0_5_第10班</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>609_0_5_第11班</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>609_0_5_第12班</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>609_0_5_第13班</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
